--- a/validation/expert_reviews/E2_extraction_review.xlsx
+++ b/validation/expert_reviews/E2_extraction_review.xlsx
@@ -578,7 +578,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Review workbook — Suhas</t>
+          <t>Review workbook — E2</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Grader: Suhas    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
+          <t>Grader: E2    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>Rating — Suhas</t>
+          <t>Rating — E2</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Grader: Suhas    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
+          <t>Grader: E2    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>Rating — Suhas</t>
+          <t>Rating — E2</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Grader: Suhas    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
+          <t>Grader: E2    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>Rating — Suhas</t>
+          <t>Rating — E2</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2391,7 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Grader: Suhas    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
+          <t>Grader: E2    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>Rating — Suhas</t>
+          <t>Rating — E2</t>
         </is>
       </c>
     </row>
@@ -3605,7 +3605,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Grader: Suhas    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
+          <t>Grader: E2    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
         </is>
       </c>
     </row>
@@ -3665,6 +3665,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -3780,6 +3781,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
@@ -4122,7 +4124,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Grader: Suhas    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
+          <t>Grader: E2    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
         </is>
       </c>
     </row>
@@ -4182,6 +4184,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -4297,6 +4300,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
@@ -4639,7 +4643,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Grader: Suhas    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
+          <t>Grader: E2    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
         </is>
       </c>
     </row>
@@ -4699,6 +4703,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -4814,6 +4819,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
@@ -5156,7 +5162,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Grader: Suhas    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
+          <t>Grader: E2    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
         </is>
       </c>
     </row>
@@ -5216,6 +5222,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -5331,6 +5338,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
@@ -5673,7 +5681,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Grader: Suhas    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
+          <t>Grader: E2    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
         </is>
       </c>
     </row>
@@ -5733,6 +5741,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -5848,6 +5857,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
@@ -6190,7 +6200,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Grader: Suhas    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
+          <t>Grader: E2    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
         </is>
       </c>
     </row>
@@ -6250,6 +6260,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -6365,6 +6376,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
@@ -6712,7 +6724,7 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Grader: Suhas    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
+          <t>Grader: E2    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
         </is>
       </c>
     </row>
@@ -6731,7 +6743,7 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>Rating — Suhas</t>
+          <t>Rating — E2</t>
         </is>
       </c>
     </row>
@@ -7148,7 +7160,7 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Grader: Suhas    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
+          <t>Grader: E2    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7179,7 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>Rating — Suhas</t>
+          <t>Rating — E2</t>
         </is>
       </c>
     </row>
